--- a/data/trans_camb/IMC_inf_R2-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IMC_inf_R2-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-19,75; 19,19</t>
+          <t>-20,55; 18,87</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-25,15; 14,86</t>
+          <t>-22,41; 16,51</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-34,32; 6,13</t>
+          <t>-33,58; 5,64</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-23,09; 16,04</t>
+          <t>-22,42; 15,93</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-16,44; 19,34</t>
+          <t>-17,57; 18,21</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-34,07; 5,81</t>
+          <t>-36,45; 5,89</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-15,29; 12,47</t>
+          <t>-16,32; 11,99</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-15,04; 11,65</t>
+          <t>-16,22; 10,59</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-28,53; 1,22</t>
+          <t>-29,12; -0,81</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-33,47; 51,39</t>
+          <t>-35,65; 47,74</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-42,12; 39,07</t>
+          <t>-38,73; 44,11</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-58,97; 18,42</t>
+          <t>-58,71; 12,86</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-40,33; 39,75</t>
+          <t>-40,68; 36,35</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-30,21; 45,24</t>
+          <t>-30,77; 43,59</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-62,13; 14,06</t>
+          <t>-65,59; 11,46</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-28,14; 29,37</t>
+          <t>-28,89; 27,39</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-26,09; 27,18</t>
+          <t>-28,46; 23,57</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-53,27; 3,18</t>
+          <t>-53,1; -1,48</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,46; 9,84</t>
+          <t>-5,94; 9,4</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-11,19; 3,47</t>
+          <t>-12,18; 3,5</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-14,01; 3,52</t>
+          <t>-13,86; 3,02</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8,12; 23,19</t>
+          <t>8,4; 23,51</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 11,88</t>
+          <t>-3,35; 11,45</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,95; 10,44</t>
+          <t>-6,36; 9,89</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,61; 14,53</t>
+          <t>3,64; 15,03</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,68; 5,79</t>
+          <t>-4,68; 6,2</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-7,28; 5,08</t>
+          <t>-7,12; 4,87</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-11,66; 23,36</t>
+          <t>-12,49; 23,57</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-23,28; 8,13</t>
+          <t>-25,7; 8,8</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-29,41; 8,3</t>
+          <t>-29,74; 7,11</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16,36; 56,45</t>
+          <t>17,24; 56,83</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-6,72; 28,82</t>
+          <t>-6,93; 28,19</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-14,25; 25,11</t>
+          <t>-12,99; 23,87</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,14; 34,74</t>
+          <t>7,62; 35,9</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-10,02; 13,81</t>
+          <t>-9,91; 14,6</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-15,67; 11,93</t>
+          <t>-15,5; 11,57</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 19,79</t>
+          <t>-0,09; 20,32</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-12,86; 5,69</t>
+          <t>-12,64; 6,09</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-16,26; 3,64</t>
+          <t>-16,32; 4,12</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-10,34; 9,42</t>
+          <t>-10,56; 9,08</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-10,86; 7,98</t>
+          <t>-9,67; 9,31</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-19,58; 0,67</t>
+          <t>-17,5; 2,16</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 11,61</t>
+          <t>-3,2; 11,25</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-8,59; 4,78</t>
+          <t>-8,48; 4,98</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-13,83; -0,5</t>
+          <t>-14,1; 0,09</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,03; 54,65</t>
+          <t>0,46; 57,82</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-27,33; 15,95</t>
+          <t>-27,12; 17,3</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-35,0; 9,38</t>
+          <t>-35,09; 11,66</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-18,52; 20,51</t>
+          <t>-19,19; 20,27</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-19,22; 17,63</t>
+          <t>-17,2; 20,49</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-35,76; 1,63</t>
+          <t>-32,94; 4,36</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 28,09</t>
+          <t>-6,49; 25,95</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-17,29; 11,23</t>
+          <t>-17,04; 12,22</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-27,81; -1,45</t>
+          <t>-28,26; 0,95</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,68; 17,18</t>
+          <t>2,92; 16,59</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 11,55</t>
+          <t>-2,46; 10,88</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-8,29; 7,0</t>
+          <t>-7,76; 5,93</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-11,93; 4,68</t>
+          <t>-11,84; 5,32</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-19,07; -1,45</t>
+          <t>-18,84; -1,21</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-17,61; 0,34</t>
+          <t>-17,78; 0,06</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 8,4</t>
+          <t>-2,81; 8,22</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-9,28; 1,99</t>
+          <t>-8,52; 3,1</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-10,62; 1,4</t>
+          <t>-10,73; 1,19</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>11,56; 116,98</t>
+          <t>12,67; 115,43</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-11,93; 82,71</t>
+          <t>-13,37; 76,33</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-40,16; 46,0</t>
+          <t>-38,14; 38,59</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-26,6; 12,82</t>
+          <t>-27,35; 14,24</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-42,44; -3,98</t>
+          <t>-41,1; -2,94</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-39,69; 1,49</t>
+          <t>-40,29; 0,11</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-8,69; 29,95</t>
+          <t>-8,98; 30,29</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-29,27; 7,49</t>
+          <t>-26,81; 11,08</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-33,2; 5,19</t>
+          <t>-33,41; 4,48</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,48; 11,51</t>
+          <t>2,04; 11,6</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,92; 4,31</t>
+          <t>-5,07; 4,02</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-12,89; -1,84</t>
+          <t>-12,44; -1,78</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,19; 10,03</t>
+          <t>0,19; 9,63</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-5,13; 4,46</t>
+          <t>-5,29; 4,11</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-11,87; -1,14</t>
+          <t>-11,59; -1,2</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,21; 9,16</t>
+          <t>2,4; 9,1</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 2,5</t>
+          <t>-3,72; 3,11</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-10,41; -2,69</t>
+          <t>-10,27; -2,84</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>6,62; 35,38</t>
+          <t>5,64; 35,67</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-13,21; 13,13</t>
+          <t>-13,37; 12,2</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-34,68; -5,62</t>
+          <t>-33,62; -5,68</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>0,06; 22,95</t>
+          <t>0,52; 22,72</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-10,85; 10,07</t>
+          <t>-11,35; 9,58</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-25,02; -2,62</t>
+          <t>-24,39; -2,83</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,25; 23,49</t>
+          <t>5,61; 23,41</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-9,02; 6,44</t>
+          <t>-8,93; 7,99</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-25,15; -7,02</t>
+          <t>-24,7; -7,04</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IMC_inf_R2-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IMC_inf_R2-Edad-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con sobrepeso u obesidad declarado</t>
+          <t>Población con sobrepeso u obesidad declarado por los/as progenitores/as</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-20,55; 18,87</t>
+          <t>-18,52; 20,74</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-22,41; 16,51</t>
+          <t>-23,94; 15,7</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-33,58; 5,64</t>
+          <t>-32,15; 7,72</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-22,42; 15,93</t>
+          <t>-22,98; 17,43</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-17,57; 18,21</t>
+          <t>-18,9; 19,95</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-36,45; 5,89</t>
+          <t>-34,03; 5,87</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-16,32; 11,99</t>
+          <t>-16,3; 11,06</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-16,22; 10,59</t>
+          <t>-14,36; 11,09</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-29,12; -0,81</t>
+          <t>-30,34; -1,02</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-35,65; 47,74</t>
+          <t>-31,86; 54,48</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-38,73; 44,11</t>
+          <t>-39,91; 40,07</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-58,71; 12,86</t>
+          <t>-56,62; 18,24</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-40,68; 36,35</t>
+          <t>-39,93; 44,92</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-30,77; 43,59</t>
+          <t>-32,44; 47,62</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-65,59; 11,46</t>
+          <t>-61,41; 16,11</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-28,89; 27,39</t>
+          <t>-29,25; 24,6</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-28,46; 23,57</t>
+          <t>-26,35; 24,7</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-53,1; -1,48</t>
+          <t>-53,49; -2,19</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,94; 9,4</t>
+          <t>-6,1; 10,33</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-12,18; 3,5</t>
+          <t>-11,66; 3,69</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-13,86; 3,02</t>
+          <t>-13,2; 4,3</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8,4; 23,51</t>
+          <t>7,63; 23,44</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 11,45</t>
+          <t>-3,35; 11,99</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,36; 9,89</t>
+          <t>-6,77; 10,32</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,64; 15,03</t>
+          <t>3,55; 14,77</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,68; 6,2</t>
+          <t>-4,85; 5,99</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-7,12; 4,87</t>
+          <t>-7,31; 4,3</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-12,49; 23,57</t>
+          <t>-12,4; 25,52</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-25,7; 8,8</t>
+          <t>-24,93; 9,09</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-29,74; 7,11</t>
+          <t>-27,8; 10,54</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17,24; 56,83</t>
+          <t>15,9; 57,95</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-6,93; 28,19</t>
+          <t>-6,9; 28,57</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-12,99; 23,87</t>
+          <t>-13,47; 25,22</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,62; 35,9</t>
+          <t>7,11; 34,75</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-9,91; 14,6</t>
+          <t>-10,24; 14,01</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-15,5; 11,57</t>
+          <t>-15,65; 9,77</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 20,32</t>
+          <t>0,75; 20,73</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-12,64; 6,09</t>
+          <t>-12,5; 6,49</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-16,32; 4,12</t>
+          <t>-15,6; 4,29</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-10,56; 9,08</t>
+          <t>-11,23; 8,81</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-9,67; 9,31</t>
+          <t>-9,94; 8,8</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-17,5; 2,16</t>
+          <t>-18,78; 1,17</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 11,25</t>
+          <t>-3,16; 10,99</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-8,48; 4,98</t>
+          <t>-8,42; 4,48</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-14,1; 0,09</t>
+          <t>-13,78; -0,27</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,46; 57,82</t>
+          <t>1,83; 57,98</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-27,12; 17,3</t>
+          <t>-26,07; 17,25</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-35,09; 11,66</t>
+          <t>-33,55; 11,16</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-19,19; 20,27</t>
+          <t>-19,85; 19,18</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-17,2; 20,49</t>
+          <t>-17,89; 19,36</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-32,94; 4,36</t>
+          <t>-34,62; 2,69</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-6,49; 25,95</t>
+          <t>-6,22; 25,78</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-17,04; 12,22</t>
+          <t>-16,86; 10,63</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-28,26; 0,95</t>
+          <t>-27,95; -0,69</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,92; 16,59</t>
+          <t>2,14; 17,07</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 10,88</t>
+          <t>-3,0; 11,5</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-7,76; 5,93</t>
+          <t>-7,87; 6,29</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-11,84; 5,32</t>
+          <t>-12,15; 4,52</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-18,84; -1,21</t>
+          <t>-17,87; -1,34</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-17,78; 0,06</t>
+          <t>-18,34; -0,2</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 8,22</t>
+          <t>-2,94; 7,9</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-8,52; 3,1</t>
+          <t>-8,69; 1,75</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-10,73; 1,19</t>
+          <t>-10,8; 1,15</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>12,67; 115,43</t>
+          <t>11,2; 118,89</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-13,37; 76,33</t>
+          <t>-15,89; 77,71</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-38,14; 38,59</t>
+          <t>-39,17; 43,26</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-27,35; 14,24</t>
+          <t>-27,43; 11,65</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-41,1; -2,94</t>
+          <t>-40,12; -3,01</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-40,29; 0,11</t>
+          <t>-40,69; -0,46</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-8,98; 30,29</t>
+          <t>-9,01; 28,74</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-26,81; 11,08</t>
+          <t>-27,25; 7,09</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-33,41; 4,48</t>
+          <t>-33,81; 4,09</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,04; 11,6</t>
+          <t>1,83; 11,66</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-5,07; 4,02</t>
+          <t>-5,25; 4,14</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-12,44; -1,78</t>
+          <t>-12,63; -2,38</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,19; 9,63</t>
+          <t>0,55; 9,92</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-5,29; 4,11</t>
+          <t>-5,36; 3,84</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-11,59; -1,2</t>
+          <t>-11,85; -1,55</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,4; 9,1</t>
+          <t>2,56; 9,3</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 3,11</t>
+          <t>-3,83; 2,57</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-10,27; -2,84</t>
+          <t>-10,42; -2,97</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>5,64; 35,67</t>
+          <t>4,78; 34,78</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-13,37; 12,2</t>
+          <t>-14,07; 12,54</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-33,62; -5,68</t>
+          <t>-33,49; -5,96</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>0,52; 22,72</t>
+          <t>1,27; 23,1</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-11,35; 9,58</t>
+          <t>-11,06; 8,93</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-24,39; -2,83</t>
+          <t>-24,43; -3,51</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,61; 23,41</t>
+          <t>6,45; 24,29</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-8,93; 7,99</t>
+          <t>-9,11; 6,6</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-24,7; -7,04</t>
+          <t>-24,83; -7,7</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IMC_inf_R2-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IMC_inf_R2-Edad-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-3,57</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0,03</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-15,57</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-0,26</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-4,15</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-14,14</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-3,57</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,03</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-16,22</t>
+          <t>-14,81</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-15,05</t>
+          <t>-15,13</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-18,52; 20,74</t>
+          <t>-23,09; 16,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-23,94; 15,7</t>
+          <t>-16,44; 19,34</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-32,15; 7,72</t>
+          <t>-34,11; 5,92</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-22,98; 17,43</t>
+          <t>-19,75; 19,19</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-18,9; 19,95</t>
+          <t>-25,15; 14,86</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-34,03; 5,87</t>
+          <t>-34,9; 5,18</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-16,3; 11,06</t>
+          <t>-15,29; 12,47</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-14,36; 11,09</t>
+          <t>-15,04; 11,65</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-30,34; -1,02</t>
+          <t>-28,92; 0,53</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-7,12%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0,05%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-31,08%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-0,51%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-8,3%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-28,27%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-7,12%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0,05%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-32,37%</t>
+          <t>-29,62%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-30,07%</t>
+          <t>-30,22%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-31,86; 54,48</t>
+          <t>-40,33; 39,75</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-39,91; 40,07</t>
+          <t>-30,21; 45,24</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-56,62; 18,24</t>
+          <t>-61,74; 14,83</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-39,93; 44,92</t>
+          <t>-33,47; 51,39</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-32,44; 47,62</t>
+          <t>-42,12; 39,07</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-61,41; 16,11</t>
+          <t>-60,92; 15,82</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-29,25; 24,6</t>
+          <t>-28,14; 29,37</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-26,35; 24,7</t>
+          <t>-26,09; 27,18</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-53,49; -2,19</t>
+          <t>-52,6; 1,79</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>15,75</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>3,92</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1,96</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>1,6</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-3,89</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-5,33</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>15,75</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>3,92</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,92</t>
+          <t>-7,15</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-1,31</t>
+          <t>-2,26</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,1; 10,33</t>
+          <t>8,12; 23,19</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-11,66; 3,69</t>
+          <t>-3,24; 11,88</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-13,2; 4,3</t>
+          <t>-6,84; 10,57</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,63; 23,44</t>
+          <t>-5,46; 9,84</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 11,99</t>
+          <t>-11,19; 3,47</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,77; 10,32</t>
+          <t>-15,33; 1,4</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,55; 14,77</t>
+          <t>3,61; 14,53</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,85; 5,99</t>
+          <t>-4,68; 5,79</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-7,31; 4,3</t>
+          <t>-8,13; 3,69</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>34,94%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>8,7%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>4,34%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>3,6%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-8,78%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-12,02%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>34,94%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>8,7%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>-16,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-2,93%</t>
+          <t>-5,06%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-12,4; 25,52</t>
+          <t>16,36; 56,45</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-24,93; 9,09</t>
+          <t>-6,72; 28,82</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-27,8; 10,54</t>
+          <t>-13,67; 24,84</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15,9; 57,95</t>
+          <t>-11,66; 23,36</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-6,9; 28,57</t>
+          <t>-23,28; 8,13</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-13,47; 25,22</t>
+          <t>-32,4; 3,58</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,11; 34,75</t>
+          <t>8,14; 34,74</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-10,24; 14,01</t>
+          <t>-10,02; 13,81</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-15,65; 9,77</t>
+          <t>-17,42; 8,98</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-1,19</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-0,43</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-8,4</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>10,5</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-3,06</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-6,37</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-1,19</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-0,43</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-8,6</t>
+          <t>-7,16</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-7,42</t>
+          <t>-7,76</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,75; 20,73</t>
+          <t>-10,34; 9,42</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-12,5; 6,49</t>
+          <t>-10,86; 7,98</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-15,6; 4,29</t>
+          <t>-19,19; 0,74</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-11,23; 8,81</t>
+          <t>-0,03; 19,79</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-9,94; 8,8</t>
+          <t>-12,86; 5,69</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-18,78; 1,17</t>
+          <t>-16,67; 1,89</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 10,99</t>
+          <t>-1,89; 11,61</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-8,42; 4,48</t>
+          <t>-8,59; 4,78</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-13,78; -0,27</t>
+          <t>-14,08; -1,24</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-2,35%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-0,86%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-16,63%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>25,04%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-7,29%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-15,19%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-2,35%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-0,86%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-17,02%</t>
+          <t>-17,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-16,0%</t>
+          <t>-16,75%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,83; 57,98</t>
+          <t>-18,52; 20,51</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-26,07; 17,25</t>
+          <t>-19,22; 17,63</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-33,55; 11,16</t>
+          <t>-35,32; 1,88</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-19,85; 19,18</t>
+          <t>0,03; 54,65</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-17,89; 19,36</t>
+          <t>-27,33; 15,95</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-34,62; 2,69</t>
+          <t>-35,64; 4,62</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-6,22; 25,78</t>
+          <t>-3,73; 28,09</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-16,86; 10,63</t>
+          <t>-17,29; 11,23</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-27,95; -0,69</t>
+          <t>-28,04; -2,91</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-3,77</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-10,14</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-7,94</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>9,42</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>4,07</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-0,54</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-3,77</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-10,14</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-8,98</t>
+          <t>1,05</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-4,67</t>
+          <t>-3,22</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,14; 17,07</t>
+          <t>-11,93; 4,68</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,0; 11,5</t>
+          <t>-19,07; -1,45</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-7,87; 6,29</t>
+          <t>-16,38; 1,49</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-12,15; 4,52</t>
+          <t>2,68; 17,18</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-17,87; -1,34</t>
+          <t>-2,35; 11,55</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-18,34; -0,2</t>
+          <t>-5,48; 8,07</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 7,9</t>
+          <t>-2,7; 8,4</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-8,69; 1,75</t>
+          <t>-9,28; 1,99</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-10,8; 1,15</t>
+          <t>-8,61; 2,47</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-9,08%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-24,43%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-19,13%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>54,11%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>23,37%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-3,11%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-9,08%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-24,43%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-21,62%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-15,66%</t>
+          <t>-10,81%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>11,2; 118,89</t>
+          <t>-26,6; 12,82</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-15,89; 77,71</t>
+          <t>-42,44; -3,98</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-39,17; 43,26</t>
+          <t>-36,76; 4,31</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-27,43; 11,65</t>
+          <t>11,56; 116,98</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-40,12; -3,01</t>
+          <t>-11,93; 82,71</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-40,69; -0,46</t>
+          <t>-26,24; 57,1</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-9,01; 28,74</t>
+          <t>-8,69; 29,95</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-27,25; 7,09</t>
+          <t>-29,27; 7,49</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-33,81; 4,09</t>
+          <t>-27,27; 9,32</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>5,06</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-0,69</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>-6,05</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>6,91</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>-0,37</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-6,91</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>5,06</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-0,69</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-6,42</t>
+          <t>-6,7</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-6,45</t>
+          <t>-6,2</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,83; 11,66</t>
+          <t>0,19; 10,03</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-5,25; 4,14</t>
+          <t>-5,13; 4,46</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-12,63; -2,38</t>
+          <t>-11,69; -1,08</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,55; 9,92</t>
+          <t>2,48; 11,51</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-5,36; 3,84</t>
+          <t>-4,92; 4,31</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-11,85; -1,55</t>
+          <t>-11,13; -2,09</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,56; 9,3</t>
+          <t>2,21; 9,16</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 2,57</t>
+          <t>-3,78; 2,5</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-10,42; -2,97</t>
+          <t>-9,67; -2,94</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>11,15%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-1,52%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-13,31%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>19,61%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>-1,04%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-19,61%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>11,15%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-1,52%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-14,14%</t>
+          <t>-19,02%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-15,94%</t>
+          <t>-15,32%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>4,78; 34,78</t>
+          <t>0,06; 22,95</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-14,07; 12,54</t>
+          <t>-10,85; 10,07</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-33,49; -5,96</t>
+          <t>-24,75; -2,61</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1,27; 23,1</t>
+          <t>6,62; 35,38</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-11,06; 8,93</t>
+          <t>-13,21; 13,13</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-24,43; -3,51</t>
+          <t>-29,92; -6,45</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>6,45; 24,29</t>
+          <t>5,25; 23,49</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-9,11; 6,6</t>
+          <t>-9,02; 6,44</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-24,83; -7,7</t>
+          <t>-23,14; -7,25</t>
         </is>
       </c>
     </row>
